--- a/exports/treasury/treasury_flyTradesRecap.xlsx
+++ b/exports/treasury/treasury_flyTradesRecap.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -60,7 +60,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -193,16 +193,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -549,7 +549,7 @@
       </c>
     </row>
     <row r="4" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -561,7 +561,7 @@
       <c r="E4" s="3">
         <v>1.7101</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="7">
         <v>0.51900000000000002</v>
       </c>
       <c r="G4" s="4">
@@ -569,7 +569,7 @@
       </c>
     </row>
     <row r="5" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
@@ -581,7 +581,7 @@
       <c r="E5" s="3">
         <v>2.5884999999999998</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="7">
         <v>0.28410000000000002</v>
       </c>
       <c r="G5" s="4">
@@ -589,7 +589,7 @@
       </c>
     </row>
     <row r="6" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -601,7 +601,7 @@
       <c r="E6" s="3">
         <v>1.9055</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="7">
         <v>0.32990000000000003</v>
       </c>
       <c r="G6" s="4">
@@ -609,7 +609,7 @@
       </c>
     </row>
     <row r="7" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -621,7 +621,7 @@
       <c r="E7" s="3">
         <v>1.9919</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="7">
         <v>0.37140000000000001</v>
       </c>
       <c r="G7" s="4">
@@ -629,7 +629,7 @@
       </c>
     </row>
     <row r="8" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -641,7 +641,7 @@
       <c r="E8" s="3">
         <v>3.778</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="7">
         <v>0.50239999999999996</v>
       </c>
       <c r="G8" s="4">
@@ -649,7 +649,7 @@
       </c>
     </row>
     <row r="9" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -661,7 +661,7 @@
       <c r="E9" s="3">
         <v>4.5796999999999999</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="7">
         <v>0.51849999999999996</v>
       </c>
       <c r="G9" s="4">
@@ -669,7 +669,7 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -681,7 +681,7 @@
       <c r="E10" s="3">
         <v>3.3407</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="7">
         <v>0.51719999999999999</v>
       </c>
       <c r="G10" s="4">
@@ -689,7 +689,7 @@
       </c>
     </row>
     <row r="11" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -701,7 +701,7 @@
       <c r="E11" s="3">
         <v>3.2000999999999999</v>
       </c>
-      <c r="F11" s="8">
+      <c r="F11" s="7">
         <v>0.5</v>
       </c>
       <c r="G11" s="4">
@@ -709,7 +709,7 @@
       </c>
     </row>
     <row r="12" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -721,7 +721,7 @@
       <c r="E12" s="3">
         <v>2.8325</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="7">
         <v>0.47749999999999998</v>
       </c>
       <c r="G12" s="4">
@@ -729,7 +729,7 @@
       </c>
     </row>
     <row r="13" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -741,7 +741,7 @@
       <c r="E13" s="3">
         <v>2.8052000000000001</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F13" s="7">
         <v>0.38569999999999999</v>
       </c>
       <c r="G13" s="4">
@@ -749,7 +749,7 @@
       </c>
     </row>
     <row r="14" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -761,7 +761,7 @@
       <c r="E14" s="3">
         <v>2.7290999999999999</v>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="7">
         <v>0.54549999999999998</v>
       </c>
       <c r="G14" s="4">
@@ -770,12 +770,12 @@
     </row>
     <row r="15" spans="2:7" ht="5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="16" spans="2:7" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="2">
